--- a/AL_year1_awardees.xlsx
+++ b/AL_year1_awardees.xlsx
@@ -165,7 +165,7 @@
     <t xml:space="preserve">IN_KIND_BENEFIT</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: statewide FQHC membership association, not itself a health center. §10.2 IN_KIND_BENEFIT: the recipient is not a hospital and keeps the funds; hospitals use or are served by what the funds build. These dollars must never enter a 'funds distributed to hospitals' total. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Curated override: statewide FQHC membership association, not itself a health center. §10.2 IN_KIND_BENEFIT: the recipient is not a hospital and keeps the funds, and the source names hospitals among the parties the funded work serves. These dollars must never enter a 'funds distributed to hospitals' total; they are kept visible rather than discarded. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/AL/2026-08-24_governor_ivey_first_arhtp_grants.html</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">NON_HOSPITAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: community mental health provider; it operates psychiatric hospitals, but the release does not state which entity received the grant -- confirm before coding as a hospital. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Curated override: community mental health provider; it operates psychiatric hospitals, but the release does not state which entity received the grant -- confirm before coding as a hospital. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Baldwin, Clay, Coosa, Mobile, Randolph, Talladega, Washington</t>
@@ -222,7 +222,7 @@
     <t xml:space="preserve">AMOUNT_ROUNDED_IN_SOURCE</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 IN_KIND_BENEFIT: the recipient is not a hospital and keeps the funds; hospitals use or are served by what the funds build. These dollars must never enter a 'funds distributed to hospitals' total. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">ROUNDED_TO_MILLIONS</t>
@@ -243,7 +243,7 @@
     <t xml:space="preserve">PHYSICIAN_PRACTICE</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: professional corporation suffix. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Recipient name rule: professional corporation suffix. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -258,7 +258,7 @@
     <t xml:space="preserve">FQHC_OR_RHC</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: federally qualified health center; one of its own awards establishes a further FQHC site. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Curated override: federally qualified health center; one of its own awards establishes a further FQHC site. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Bibb, Chilton, Dallas, Marengo, Perry, Wilcox</t>
@@ -309,7 +309,7 @@
     <t xml:space="preserve">EMS_OR_PSAP</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states an EMS entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Recipient name rule: name states an EMS entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Bullock, Covington, Crenshaw, Elmore, Lowndes, Macon, Pike, Tallapoosa</t>
@@ -351,7 +351,7 @@
     <t xml:space="preserve">RECIPIENT_TYPE_INFERRED</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">FALLBACK</t>
@@ -366,7 +366,7 @@
     <t xml:space="preserve">LOCAL_GOVT_OR_PUBLIC_HEALTH</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: county mental health board, a public body. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Curated override: county mental health board, a public body. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Mental Health Board of Chilton and Shelby Counties Inc. DBA Central Alabama Wellness – $43,580 to upgrade its electronic health record system to improve care coordination, patient access and information sharing across behavioral health and other healthcare providers in Chilton and Shelby counties.</t>
@@ -393,7 +393,7 @@
     <t xml:space="preserve">Collaborative Electronic Health Record (EHR), IT and Cybersecurity Initiative | second grant to this recipient under this initiative</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states an EMS entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
+    <t xml:space="preserve">Recipient name rule: name states an EMS entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
   </si>
   <si>
     <t xml:space="preserve">SECOND</t>
@@ -414,7 +414,7 @@
     <t xml:space="preserve">Clair Community Health Clinic Inc.</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: free clinic for uninsured rural adults in St. Clair County; the release publishes the name without its leading 'St.'. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Curated override: free clinic for uninsured rural adults in St. Clair County; the release publishes the name without its leading 'St.'. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">Clair Community Health Clinic Inc. – $1.17 million to upgrade its electronic health record, pharmacy, cybersecurity and digital infrastructure to improve care coordination, protect patient information and support more efficient care for uninsured rural adults in St. Clair County.</t>
@@ -435,7 +435,7 @@
     <t xml:space="preserve">TLC Pediatrics &amp; Family</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a clinical practice. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Recipient name rule: name states a clinical practice. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">TLC Pediatrics &amp; Family – $200,000 to enhance its information technology and cybersecurity systems to protect patient information and maintain reliable access to care in Limestone County.</t>
@@ -477,9 +477,6 @@
     <t xml:space="preserve">The University of Alabama</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cullman, Fayette, Greene, Hale, Lee, Marengo, Montgomery, Pickens, Sumter, Talladega, Tallapoosa, Tuscaloosa</t>
   </si>
   <si>
@@ -489,6 +486,9 @@
     <t xml:space="preserve">University of South Alabama</t>
   </si>
   <si>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 IN_KIND_BENEFIT: the recipient is not a hospital and keeps the funds, and the source names hospitals among the parties the funded work serves. These dollars must never enter a 'funds distributed to hospitals' total; they are kept visible rather than discarded. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Butler, Choctaw, Clarke, Conecuh, Covington, Crenshaw, Dallas, Escambia, Greene, Hale, Lowndes, Marengo, Monroe, Perry, Sumter, Washington, Wilcox</t>
   </si>
   <si>
@@ -504,7 +504,7 @@
     <t xml:space="preserve">Whatley Health Services Inc.</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: federally qualified health center network. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Curated override: federally qualified health center network. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">Greene, Hale, Lamar, Pickens, Sumter, Tuscaloosa, Walker</t>
@@ -561,7 +561,7 @@
     <t xml:space="preserve">The Arc of Madison County, Inc.</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">Madison, Shelby, Walker</t>
@@ -591,7 +591,7 @@
     <t xml:space="preserve">Cahaba Medical Care Foundation – This healthcare institution has received two grants under this initiative, including one for $106,500 to establish a two-tier telehealth and specialty consultation program across six rural clinics to expand access to dermatology services closer to home (Bibb, Chilton, Perry, Wilcox).</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: federally qualified health center; one of its own awards establishes a further FQHC site. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
+    <t xml:space="preserve">Curated override: federally qualified health center; one of its own awards establishes a further FQHC site. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
   </si>
   <si>
     <t xml:space="preserve">Bibb, Dallas, Marengo, Perry, Wilcox</t>
@@ -702,7 +702,7 @@
     <t xml:space="preserve">Floyd Healthcare Management DBA Atrium Health Floyd EMS</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: the DBA names the hospital's EMS division, which is the recipient. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Curated override: the DBA names the hospital's EMS division, which is the recipient. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Calhoun, Cherokee</t>
@@ -714,7 +714,7 @@
     <t xml:space="preserve">Franklin Primary Health Center Inc.</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: community/primary health center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Recipient name rule: community/primary health center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Baldwin, Choctaw, Conecuh, Escambia, Monroe</t>
@@ -843,7 +843,7 @@
     <t xml:space="preserve">TRIBAL_ORG</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a tribal entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Recipient name rule: name states a tribal entity. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Escambia</t>
@@ -951,7 +951,7 @@
     <t xml:space="preserve">TLC Pediatrics &amp; Family – This medical clinic has received two grants under this initiative, including one for $174,117 to establish the Rural Maternal-Infant Wellness and Lactation Access Program by hiring a full-time certified breastfeeding specialist and creating a dedicated space for breastfeeding and family support (Limestone).</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a clinical practice. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
+    <t xml:space="preserve">Recipient name rule: name states a clinical practice. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
   </si>
   <si>
     <t xml:space="preserve">A second grant for $33,508 will help establish the Rural Newborn Screening and Early Childhood Development Initiative to provide in-clinic newborn jaundice screening and standardized developmental and social-emotional screenings during routine pediatric visits (Limestone).</t>
@@ -987,7 +987,7 @@
     <t xml:space="preserve">UAB Montgomery</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: UAB's Montgomery regional medical campus; the name carries no university token. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Curated override: UAB's Montgomery regional medical campus; the name carries no university token. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">Lowndes</t>
@@ -1032,7 +1032,7 @@
     <t xml:space="preserve">Rural Workforce Initiative</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Alabama Community College System – The system received two grants from this initiative, including $464,000 to establish a statewide training network that awards college credit for qualifying military training and creates accelerated pathways for veterans to complete healthcare credentials.</t>
@@ -1041,7 +1041,7 @@
     <t xml:space="preserve">Rural Workforce Initiative | second grant to this recipient under this initiative</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
+    <t xml:space="preserve">Recipient name rule: name states a university or college. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
   </si>
   <si>
     <t xml:space="preserve">Baldwin, Coffee, Colbert, Conecuh, Covington, Cullman, Dallas, DeKalb, Etowah, Houston, Jefferson, Limestone, Madison, Marshall, Mobile, Montgomery, Randolph, Russell, Tallapoosa, Tuscaloosa, Walker</t>
@@ -1116,7 +1116,7 @@
     <t xml:space="preserve">Faulkner University – $975,000 to establish a rural healthcare workforce program that provides tuition assistance to eligible health profession students who commit to five years of employment in rural Alabama and support housing, travel and related costs for students completing rural clinical rotations in 58 counties (Baldwin, Barbour, Bibb, Blount, Bullock, Butler, Calhoun, Chambers, Cherokee, Chilton, Choctaw, Clarke, Clay, Cleburne, Coffee, Conecuh, Coosa, Covington, Crenshaw, Cullman, Dale, Dallas, DeKalb, Elmore, Escambia, Etowah, Fayette, Franklin, Geneva, Greene, Hale, Henry, Jackson, Lamar, Lauderdale, Lawrence, Limestone, Lowndes, Macon, Marengo, Marion, Marshall, Mobile, Monroe, Morgan, Perry, Pickens, Pike, Randolph, Shelby, St. Clair, Sumter, Talladega, Tallapoosa, Walker, Washington, Wilcox, Winston).</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: community/primary health center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Recipient name rule: community/primary health center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">Franklin Primary Health Center Inc. – $1.1 million to expand its accredited family medicine residency program by developing a rural training track to strengthen the pipeline of primary care physicians prepared to practice in rural communities in Baldwin County.</t>
@@ -1149,7 +1149,7 @@
     <t xml:space="preserve">Regional Training Institute</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: training body; organisational form not stated by the source. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Curated override: training body; organisational form not stated by the source. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">Bibb, Blount, Calhoun, Chambers, Cherokee, Chilton, Coosa, Covington, Crenshaw, Cullman, Dallas, DeKalb, Elmore, Etowah, Fayette, Franklin, Hale, Jackson, Jefferson, Lamar, Lawrence, Limestone, Lowndes, Macon, Marengo, Marion, Marshall, Morgan, Perry, Pickens, Randolph, Shelby, St. Clair, Talladega, Walker, Winston</t>
@@ -1215,7 +1215,7 @@
     <t xml:space="preserve">Rural Health Practice Initiative</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: community mental health provider; it operates psychiatric hospitals, but the release does not state which entity received the grant -- confirm before coding as a hospital. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Curated override: community mental health provider; it operates psychiatric hospitals, but the release does not state which entity received the grant -- confirm before coding as a hospital. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">Clay, Talladega</t>
@@ -1242,7 +1242,7 @@
     <t xml:space="preserve">Rural Health Practice Initiative | second grant to this recipient under this initiative</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: federally qualified health center; one of its own awards establishes a further FQHC site. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
+    <t xml:space="preserve">Curated override: federally qualified health center; one of its own awards establishes a further FQHC site. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
   </si>
   <si>
     <t xml:space="preserve">A second grant for $280,579 will allow the Foundation to establish a new Federally Qualified Health Center service site in Selma by completing targeted renovations and purchasing equipment for existing medical office space (Dallas).</t>
@@ -1275,7 +1275,7 @@
     <t xml:space="preserve">Franklin Primary Health Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: federally qualified health center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Curated override: federally qualified health center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Franklin Primary Health Center – $881,190 to expand clinic-based behavioral health services across the health center’s rural primary care network to improve access to counseling, care coordination and follow-up support closer to home (Baldwin, Choctaw, Conecuh, Escambia, Monroe).</t>
@@ -1302,7 +1302,7 @@
     <t xml:space="preserve">Weiss Family Care</t>
   </si>
   <si>
-    <t xml:space="preserve">Recipient name rule: name states a clinical practice. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Recipient name rule: name states a clinical practice. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">Cherokee</t>
@@ -1329,7 +1329,7 @@
     <t xml:space="preserve">Montgomery Area Mental Health Authority DBA Carastar Health</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: area mental health authority, a public body. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
+    <t xml:space="preserve">Curated override: area mental health authority, a public body. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. The release publishes this amount rounded to millions; it is recorded as published and is not exact to the dollar.</t>
   </si>
   <si>
     <t xml:space="preserve">Elmore, Lowndes</t>
@@ -1341,7 +1341,7 @@
     <t xml:space="preserve">Southwest Alabama Behavioral Health Care Systems DBA CarePath Behavioral Health</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: community behavioral health provider; the 'Health Care Systems' token would otherwise read as a hospital system. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Curated override: community behavioral health provider; the 'Health Care Systems' token would otherwise read as a hospital system. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Clarke, Conecuh, Escambia, Monroe</t>
@@ -1371,7 +1371,7 @@
     <t xml:space="preserve">East Alabama Mental Health-Mental Retardation Board, Inc. DBA Integrea Community Mental Health System</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: county mental health board; the 'System' token would otherwise read as a hospital system. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Curated override: county mental health board; the 'System' token would otherwise read as a hospital system. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Chambers, Tallapoosa</t>
@@ -1383,7 +1383,7 @@
     <t xml:space="preserve">Jefferson-Blount-St. Clair Mental Health Authority</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: county mental health authority, a public body. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
+    <t xml:space="preserve">Curated override: county mental health authority, a public body. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties.</t>
   </si>
   <si>
     <t xml:space="preserve">Blount, Jefferson, St. Clair</t>
@@ -2217,10 +2217,10 @@
         <v>68</v>
       </c>
       <c r="W4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="X4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Y4" t="s">
         <v>69</v>
@@ -4393,7 +4393,7 @@
         <v>39</v>
       </c>
       <c r="Y26" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="Z26" t="s">
         <v>51</v>
@@ -4423,10 +4423,10 @@
         <v>56</v>
       </c>
       <c r="AI26" t="s">
+        <v>154</v>
+      </c>
+      <c r="AJ26" t="s">
         <v>155</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="27">
@@ -4437,7 +4437,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D27" t="n">
         <v>1510000</v>
@@ -4493,7 +4493,7 @@
         <v>41</v>
       </c>
       <c r="Y27" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="Z27" t="s">
         <v>51</v>
@@ -5283,7 +5283,7 @@
         <v>39</v>
       </c>
       <c r="Y35" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="Z35" t="s">
         <v>51</v>
@@ -6575,7 +6575,7 @@
         <v>39</v>
       </c>
       <c r="Y48" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="Z48" t="s">
         <v>51</v>
@@ -10131,7 +10131,7 @@
         <v>39</v>
       </c>
       <c r="Y84" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="Z84" t="s">
         <v>51</v>
@@ -10819,7 +10819,7 @@
         <v>39</v>
       </c>
       <c r="Y91" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="Z91" t="s">
         <v>51</v>
@@ -12599,7 +12599,7 @@
         <v>39</v>
       </c>
       <c r="Y109" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="Z109" t="s">
         <v>51</v>
@@ -12797,7 +12797,7 @@
         <v>39</v>
       </c>
       <c r="Y111" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="Z111" t="s">
         <v>51</v>
@@ -12897,7 +12897,7 @@
         <v>39</v>
       </c>
       <c r="Y112" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="Z112" t="s">
         <v>51</v>

--- a/AL_year1_awardees.xlsx
+++ b/AL_year1_awardees.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
   <si>
     <t xml:space="preserve">state</t>
   </si>
@@ -1065,16 +1065,7 @@
     <t xml:space="preserve">Cahaba Medical Care Foundation – The foundation received two grants from this initiative, including $100,127 to provide recruitment incentives to fourth-year medical students who enter the Cahaba+UAB Family Medicine Residency rural or frontier track and commit to at least five years of rural service in three counties (Bibb, Perry, Wilcox).</t>
   </si>
   <si>
-    <t xml:space="preserve">Unclear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELIGIBILITY_NOT_RECEIPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PASS_THROUGH_UNRESOLVED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curated override: federally qualified health center; one of its own awards establishes a further FQHC site. §10.2 PASS_THROUGH_UNRESOLVED: the recipient is not a hospital, and the source states that funds reach hospitals it does not name. §0.3 -- eligibility is not receipt -- so this is not imputed to Yes. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
+    <t xml:space="preserve">Curated override: federally qualified health center; one of its own awards establishes a further FQHC site. §10.2 IN_KIND_BENEFIT: the recipient is not a hospital and keeps the funds, and the source names hospitals among the parties the funded work serves. These dollars must never enter a 'funds distributed to hospitals' total; they are kept visible rather than discarded. Source: Governor Ivey's 2026-08-24 release, which states the awarding of 138 grants and names this recipient, amount, initiative and counties. This is the second of two grants to this recipient under this initiative; the release carries it in a continuation paragraph that names no recipient of its own.</t>
   </si>
   <si>
     <t xml:space="preserve">Bibb, Coffee, Dallas, Talladega</t>
@@ -1518,13 +1509,13 @@
     <t xml:space="preserve">rows distributed_to_hospital = Unclear</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
+    <t xml:space="preserve">0</t>
   </si>
   <si>
     <t xml:space="preserve">dollars distributed_to_hospital = Unclear</t>
   </si>
   <si>
-    <t xml:space="preserve">430,304.00</t>
+    <t xml:space="preserve">0.00</t>
   </si>
 </sst>
 </file>
@@ -10970,7 +10961,7 @@
         <v>80</v>
       </c>
       <c r="F93" t="s">
-        <v>350</v>
+        <v>39</v>
       </c>
       <c r="G93" t="s">
         <v>341</v>
@@ -11007,17 +10998,15 @@
       <c r="U93" t="s">
         <v>48</v>
       </c>
-      <c r="V93" t="s">
-        <v>351</v>
-      </c>
+      <c r="V93"/>
       <c r="W93" t="s">
-        <v>352</v>
+        <v>49</v>
       </c>
       <c r="X93" t="s">
         <v>41</v>
       </c>
       <c r="Y93" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="Z93" t="s">
         <v>51</v>
@@ -11047,10 +11036,10 @@
         <v>127</v>
       </c>
       <c r="AI93" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AJ93" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="94">
@@ -11148,7 +11137,7 @@
         <v>202</v>
       </c>
       <c r="AJ94" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95">
@@ -11159,7 +11148,7 @@
         <v>94</v>
       </c>
       <c r="C95" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D95" t="n">
         <v>3800000</v>
@@ -11245,10 +11234,10 @@
         <v>56</v>
       </c>
       <c r="AI95" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AJ95" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96">
@@ -11345,10 +11334,10 @@
         <v>56</v>
       </c>
       <c r="AI96" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="AJ96" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97">
@@ -11359,7 +11348,7 @@
         <v>96</v>
       </c>
       <c r="C97" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D97" t="n">
         <v>1500000</v>
@@ -11445,10 +11434,10 @@
         <v>56</v>
       </c>
       <c r="AI97" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AJ97" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98">
@@ -11543,10 +11532,10 @@
         <v>56</v>
       </c>
       <c r="AI98" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AJ98" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99">
@@ -11613,7 +11602,7 @@
         <v>39</v>
       </c>
       <c r="Y99" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Z99" t="s">
         <v>51</v>
@@ -11646,7 +11635,7 @@
         <v>77</v>
       </c>
       <c r="AJ99" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100">
@@ -11744,7 +11733,7 @@
         <v>77</v>
       </c>
       <c r="AJ100" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101">
@@ -11755,7 +11744,7 @@
         <v>100</v>
       </c>
       <c r="C101" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D101" t="n">
         <v>935000</v>
@@ -11842,7 +11831,7 @@
         <v>77</v>
       </c>
       <c r="AJ101" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102">
@@ -11937,10 +11926,10 @@
         <v>56</v>
       </c>
       <c r="AI102" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AJ102" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="103">
@@ -11951,7 +11940,7 @@
         <v>102</v>
       </c>
       <c r="C103" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D103" t="n">
         <v>800000</v>
@@ -12035,10 +12024,10 @@
         <v>56</v>
       </c>
       <c r="AI103" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AJ103" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104">
@@ -12049,7 +12038,7 @@
         <v>103</v>
       </c>
       <c r="C104" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D104" t="n">
         <v>1380000</v>
@@ -12105,7 +12094,7 @@
         <v>39</v>
       </c>
       <c r="Y104" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="Z104" t="s">
         <v>51</v>
@@ -12135,10 +12124,10 @@
         <v>56</v>
       </c>
       <c r="AI104" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AJ104" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="105">
@@ -12238,7 +12227,7 @@
         <v>77</v>
       </c>
       <c r="AJ105" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="106">
@@ -12336,7 +12325,7 @@
         <v>77</v>
       </c>
       <c r="AJ106" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="107">
@@ -12347,7 +12336,7 @@
         <v>106</v>
       </c>
       <c r="C107" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D107" t="n">
         <v>727000</v>
@@ -12431,10 +12420,10 @@
         <v>56</v>
       </c>
       <c r="AI107" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AJ107" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="108">
@@ -12445,7 +12434,7 @@
         <v>107</v>
       </c>
       <c r="C108" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D108" t="n">
         <v>118070</v>
@@ -12532,7 +12521,7 @@
         <v>77</v>
       </c>
       <c r="AJ108" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="109">
@@ -12543,7 +12532,7 @@
         <v>108</v>
       </c>
       <c r="C109" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D109" t="n">
         <v>7000000</v>
@@ -12629,10 +12618,10 @@
         <v>56</v>
       </c>
       <c r="AI109" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AJ109" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="110">
@@ -12643,7 +12632,7 @@
         <v>109</v>
       </c>
       <c r="C110" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D110" t="n">
         <v>887616</v>
@@ -12727,10 +12716,10 @@
         <v>127</v>
       </c>
       <c r="AI110" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AJ110" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="111">
@@ -12741,7 +12730,7 @@
         <v>110</v>
       </c>
       <c r="C111" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D111" t="n">
         <v>1470000</v>
@@ -12827,10 +12816,10 @@
         <v>56</v>
       </c>
       <c r="AI111" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AJ111" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="112">
@@ -12841,7 +12830,7 @@
         <v>111</v>
       </c>
       <c r="C112" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D112" t="n">
         <v>1250000</v>
@@ -12930,7 +12919,7 @@
         <v>158</v>
       </c>
       <c r="AJ112" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="113">
@@ -12941,7 +12930,7 @@
         <v>112</v>
       </c>
       <c r="C113" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D113" t="n">
         <v>2210000</v>
@@ -12953,7 +12942,7 @@
         <v>39</v>
       </c>
       <c r="G113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H113" t="s">
         <v>41</v>
@@ -12997,7 +12986,7 @@
         <v>39</v>
       </c>
       <c r="Y113" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="Z113" t="s">
         <v>51</v>
@@ -13018,19 +13007,19 @@
         <v>55</v>
       </c>
       <c r="AF113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH113" t="s">
         <v>56</v>
       </c>
       <c r="AI113" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AJ113" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="114">
@@ -13041,7 +13030,7 @@
         <v>113</v>
       </c>
       <c r="C114" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D114" t="n">
         <v>177961</v>
@@ -13053,7 +13042,7 @@
         <v>39</v>
       </c>
       <c r="G114" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H114" t="s">
         <v>41</v>
@@ -13116,19 +13105,19 @@
         <v>71</v>
       </c>
       <c r="AF114" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG114" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH114" t="s">
         <v>56</v>
       </c>
       <c r="AI114" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AJ114" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="115">
@@ -13151,7 +13140,7 @@
         <v>39</v>
       </c>
       <c r="G115" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H115" t="s">
         <v>41</v>
@@ -13214,19 +13203,19 @@
         <v>55</v>
       </c>
       <c r="AF115" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG115" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH115" t="s">
         <v>56</v>
       </c>
       <c r="AI115" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AJ115" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116">
@@ -13249,7 +13238,7 @@
         <v>39</v>
       </c>
       <c r="G116" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="H116" t="s">
         <v>41</v>
@@ -13291,7 +13280,7 @@
         <v>39</v>
       </c>
       <c r="Y116" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="Z116" t="s">
         <v>51</v>
@@ -13312,10 +13301,10 @@
         <v>55</v>
       </c>
       <c r="AF116" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG116" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH116" t="s">
         <v>127</v>
@@ -13324,7 +13313,7 @@
         <v>331</v>
       </c>
       <c r="AJ116" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="117">
@@ -13347,7 +13336,7 @@
         <v>39</v>
       </c>
       <c r="G117" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H117" t="s">
         <v>41</v>
@@ -13412,19 +13401,19 @@
         <v>113</v>
       </c>
       <c r="AF117" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG117" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH117" t="s">
         <v>56</v>
       </c>
       <c r="AI117" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AJ117" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="118">
@@ -13447,7 +13436,7 @@
         <v>41</v>
       </c>
       <c r="G118" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H118" t="s">
         <v>41</v>
@@ -13510,10 +13499,10 @@
         <v>71</v>
       </c>
       <c r="AF118" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG118" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH118" t="s">
         <v>56</v>
@@ -13522,7 +13511,7 @@
         <v>200</v>
       </c>
       <c r="AJ118" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="119">
@@ -13533,7 +13522,7 @@
         <v>118</v>
       </c>
       <c r="C119" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D119" t="n">
         <v>243000</v>
@@ -13545,7 +13534,7 @@
         <v>39</v>
       </c>
       <c r="G119" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H119" t="s">
         <v>41</v>
@@ -13608,19 +13597,19 @@
         <v>71</v>
       </c>
       <c r="AF119" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG119" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH119" t="s">
         <v>56</v>
       </c>
       <c r="AI119" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AJ119" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="120">
@@ -13631,7 +13620,7 @@
         <v>119</v>
       </c>
       <c r="C120" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D120" t="n">
         <v>731055</v>
@@ -13643,7 +13632,7 @@
         <v>41</v>
       </c>
       <c r="G120" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H120" t="s">
         <v>41</v>
@@ -13706,19 +13695,19 @@
         <v>71</v>
       </c>
       <c r="AF120" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG120" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH120" t="s">
         <v>56</v>
       </c>
       <c r="AI120" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AJ120" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="121">
@@ -13729,7 +13718,7 @@
         <v>120</v>
       </c>
       <c r="C121" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D121" t="n">
         <v>881190</v>
@@ -13741,7 +13730,7 @@
         <v>39</v>
       </c>
       <c r="G121" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H121" t="s">
         <v>41</v>
@@ -13783,7 +13772,7 @@
         <v>39</v>
       </c>
       <c r="Y121" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Z121" t="s">
         <v>51</v>
@@ -13804,10 +13793,10 @@
         <v>55</v>
       </c>
       <c r="AF121" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG121" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH121" t="s">
         <v>56</v>
@@ -13816,7 +13805,7 @@
         <v>234</v>
       </c>
       <c r="AJ121" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="122">
@@ -13839,7 +13828,7 @@
         <v>41</v>
       </c>
       <c r="G122" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H122" t="s">
         <v>41</v>
@@ -13902,19 +13891,19 @@
         <v>71</v>
       </c>
       <c r="AF122" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG122" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH122" t="s">
         <v>56</v>
       </c>
       <c r="AI122" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AJ122" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="123">
@@ -13937,7 +13926,7 @@
         <v>39</v>
       </c>
       <c r="G123" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H123" t="s">
         <v>41</v>
@@ -14000,10 +13989,10 @@
         <v>71</v>
       </c>
       <c r="AF123" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG123" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH123" t="s">
         <v>56</v>
@@ -14012,7 +14001,7 @@
         <v>284</v>
       </c>
       <c r="AJ123" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="124">
@@ -14023,7 +14012,7 @@
         <v>123</v>
       </c>
       <c r="C124" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D124" t="n">
         <v>60000</v>
@@ -14035,7 +14024,7 @@
         <v>39</v>
       </c>
       <c r="G124" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H124" t="s">
         <v>41</v>
@@ -14098,19 +14087,19 @@
         <v>71</v>
       </c>
       <c r="AF124" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG124" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH124" t="s">
         <v>56</v>
       </c>
       <c r="AI124" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AJ124" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="125">
@@ -14121,7 +14110,7 @@
         <v>124</v>
       </c>
       <c r="C125" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D125" t="n">
         <v>974084</v>
@@ -14133,7 +14122,7 @@
         <v>39</v>
       </c>
       <c r="G125" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H125" t="s">
         <v>41</v>
@@ -14196,10 +14185,10 @@
         <v>71</v>
       </c>
       <c r="AF125" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG125" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH125" t="s">
         <v>56</v>
@@ -14208,7 +14197,7 @@
         <v>331</v>
       </c>
       <c r="AJ125" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="126">
@@ -14219,7 +14208,7 @@
         <v>125</v>
       </c>
       <c r="C126" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D126" t="n">
         <v>1060000</v>
@@ -14231,7 +14220,7 @@
         <v>39</v>
       </c>
       <c r="G126" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H126" t="s">
         <v>41</v>
@@ -14275,7 +14264,7 @@
         <v>39</v>
       </c>
       <c r="Y126" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="Z126" t="s">
         <v>51</v>
@@ -14296,19 +14285,19 @@
         <v>71</v>
       </c>
       <c r="AF126" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG126" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AH126" t="s">
         <v>56</v>
       </c>
       <c r="AI126" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AJ126" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="127">
@@ -14319,7 +14308,7 @@
         <v>126</v>
       </c>
       <c r="C127" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D127" t="n">
         <v>935895</v>
@@ -14331,7 +14320,7 @@
         <v>39</v>
       </c>
       <c r="G127" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H127" t="s">
         <v>41</v>
@@ -14394,19 +14383,19 @@
         <v>55</v>
       </c>
       <c r="AF127" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG127" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH127" t="s">
         <v>56</v>
       </c>
       <c r="AI127" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AJ127" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="128">
@@ -14429,7 +14418,7 @@
         <v>39</v>
       </c>
       <c r="G128" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H128" t="s">
         <v>41</v>
@@ -14492,19 +14481,19 @@
         <v>55</v>
       </c>
       <c r="AF128" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG128" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH128" t="s">
         <v>56</v>
       </c>
       <c r="AI128" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AJ128" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="129">
@@ -14515,7 +14504,7 @@
         <v>128</v>
       </c>
       <c r="C129" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D129" t="n">
         <v>1040000</v>
@@ -14527,7 +14516,7 @@
         <v>39</v>
       </c>
       <c r="G129" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H129" t="s">
         <v>41</v>
@@ -14571,7 +14560,7 @@
         <v>39</v>
       </c>
       <c r="Y129" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="Z129" t="s">
         <v>51</v>
@@ -14592,19 +14581,19 @@
         <v>55</v>
       </c>
       <c r="AF129" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG129" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH129" t="s">
         <v>56</v>
       </c>
       <c r="AI129" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AJ129" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="130">
@@ -14615,7 +14604,7 @@
         <v>129</v>
       </c>
       <c r="C130" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D130" t="n">
         <v>865600</v>
@@ -14627,7 +14616,7 @@
         <v>39</v>
       </c>
       <c r="G130" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H130" t="s">
         <v>41</v>
@@ -14669,7 +14658,7 @@
         <v>39</v>
       </c>
       <c r="Y130" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="Z130" t="s">
         <v>51</v>
@@ -14690,19 +14679,19 @@
         <v>55</v>
       </c>
       <c r="AF130" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG130" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH130" t="s">
         <v>56</v>
       </c>
       <c r="AI130" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AJ130" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="131">
@@ -14725,7 +14714,7 @@
         <v>39</v>
       </c>
       <c r="G131" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H131" t="s">
         <v>41</v>
@@ -14788,19 +14777,19 @@
         <v>55</v>
       </c>
       <c r="AF131" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG131" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH131" t="s">
         <v>56</v>
       </c>
       <c r="AI131" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AJ131" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="132">
@@ -14811,7 +14800,7 @@
         <v>131</v>
       </c>
       <c r="C132" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D132" t="n">
         <v>31152</v>
@@ -14823,7 +14812,7 @@
         <v>41</v>
       </c>
       <c r="G132" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H132" t="s">
         <v>41</v>
@@ -14886,19 +14875,19 @@
         <v>71</v>
       </c>
       <c r="AF132" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG132" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH132" t="s">
         <v>56</v>
       </c>
       <c r="AI132" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AJ132" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="133">
@@ -14909,7 +14898,7 @@
         <v>132</v>
       </c>
       <c r="C133" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D133" t="n">
         <v>222347</v>
@@ -14921,7 +14910,7 @@
         <v>39</v>
       </c>
       <c r="G133" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H133" t="s">
         <v>41</v>
@@ -14986,10 +14975,10 @@
         <v>113</v>
       </c>
       <c r="AF133" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG133" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH133" t="s">
         <v>56</v>
@@ -14998,7 +14987,7 @@
         <v>196</v>
       </c>
       <c r="AJ133" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="134">
@@ -15009,7 +14998,7 @@
         <v>133</v>
       </c>
       <c r="C134" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D134" t="n">
         <v>867545</v>
@@ -15021,7 +15010,7 @@
         <v>39</v>
       </c>
       <c r="G134" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H134" t="s">
         <v>41</v>
@@ -15063,7 +15052,7 @@
         <v>39</v>
       </c>
       <c r="Y134" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="Z134" t="s">
         <v>51</v>
@@ -15084,19 +15073,19 @@
         <v>55</v>
       </c>
       <c r="AF134" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG134" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH134" t="s">
         <v>56</v>
       </c>
       <c r="AI134" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AJ134" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="135">
@@ -15107,7 +15096,7 @@
         <v>134</v>
       </c>
       <c r="C135" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D135" t="n">
         <v>542965</v>
@@ -15119,7 +15108,7 @@
         <v>39</v>
       </c>
       <c r="G135" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H135" t="s">
         <v>41</v>
@@ -15161,7 +15150,7 @@
         <v>39</v>
       </c>
       <c r="Y135" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Z135" t="s">
         <v>51</v>
@@ -15182,19 +15171,19 @@
         <v>55</v>
       </c>
       <c r="AF135" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG135" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH135" t="s">
         <v>56</v>
       </c>
       <c r="AI135" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AJ135" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="136">
@@ -15205,7 +15194,7 @@
         <v>135</v>
       </c>
       <c r="C136" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D136" t="n">
         <v>480408</v>
@@ -15217,7 +15206,7 @@
         <v>39</v>
       </c>
       <c r="G136" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H136" t="s">
         <v>41</v>
@@ -15282,19 +15271,19 @@
         <v>113</v>
       </c>
       <c r="AF136" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG136" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH136" t="s">
         <v>56</v>
       </c>
       <c r="AI136" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AJ136" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="137">
@@ -15305,7 +15294,7 @@
         <v>136</v>
       </c>
       <c r="C137" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D137" t="n">
         <v>600550</v>
@@ -15317,7 +15306,7 @@
         <v>39</v>
       </c>
       <c r="G137" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H137" t="s">
         <v>41</v>
@@ -15380,19 +15369,19 @@
         <v>71</v>
       </c>
       <c r="AF137" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG137" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH137" t="s">
         <v>56</v>
       </c>
       <c r="AI137" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AJ137" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="138">
@@ -15403,7 +15392,7 @@
         <v>137</v>
       </c>
       <c r="C138" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D138" t="n">
         <v>660527</v>
@@ -15415,7 +15404,7 @@
         <v>39</v>
       </c>
       <c r="G138" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H138" t="s">
         <v>41</v>
@@ -15457,7 +15446,7 @@
         <v>39</v>
       </c>
       <c r="Y138" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Z138" t="s">
         <v>51</v>
@@ -15478,19 +15467,19 @@
         <v>55</v>
       </c>
       <c r="AF138" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG138" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH138" t="s">
         <v>56</v>
       </c>
       <c r="AI138" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AJ138" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="139">
@@ -15501,7 +15490,7 @@
         <v>138</v>
       </c>
       <c r="C139" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D139" t="n">
         <v>86660</v>
@@ -15513,7 +15502,7 @@
         <v>39</v>
       </c>
       <c r="G139" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H139" t="s">
         <v>41</v>
@@ -15578,10 +15567,10 @@
         <v>113</v>
       </c>
       <c r="AF139" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG139" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AH139" t="s">
         <v>56</v>
@@ -15590,7 +15579,7 @@
         <v>188</v>
       </c>
       <c r="AJ139" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -15606,146 +15595,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B3" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B5" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B8" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B9" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B10" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B11" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B13" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B14" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B15" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B16" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B17" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B18" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
